--- a/data/trans_orig/IP74A4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP74A4_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto las cuotas de seguros en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de las cuotas de seguros en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
